--- a/data/trans_orig/IP07C17-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C17-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de gustarle ir al colegio en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de gustarle ir al colegio en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>8957</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19042</t>
+          <t>18877</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11836</t>
+          <t>11472</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15129</t>
+          <t>14220</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27745</t>
+          <t>27094</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,36%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11140</t>
+          <t>11405</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21980</t>
+          <t>21822</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11147</t>
+          <t>11596</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21488</t>
+          <t>21870</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25542</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40038</t>
+          <t>39407</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,16%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14845</t>
+          <t>14440</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>9274</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19256</t>
+          <t>18617</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16994</t>
+          <t>17094</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30011</t>
+          <t>30383</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>651</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>595</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>8872</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8023</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>7871</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13684</t>
+          <t>13400</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44426</t>
+          <t>45486</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64496</t>
+          <t>65937</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37190</t>
+          <t>37645</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56234</t>
+          <t>55908</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87640</t>
+          <t>86638</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114433</t>
+          <t>114367</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,05%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80476</t>
+          <t>79270</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101934</t>
+          <t>101337</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66387</t>
+          <t>66806</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89386</t>
+          <t>89791</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>153906</t>
+          <t>153750</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>184226</t>
+          <t>185710</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,55%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26378</t>
+          <t>26639</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43927</t>
+          <t>42546</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59580</t>
+          <t>59797</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>81477</t>
+          <t>82070</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>91142</t>
+          <t>91401</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120764</t>
+          <t>119951</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,42%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13241</t>
+          <t>13702</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15087</t>
+          <t>15808</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11812</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25718</t>
+          <t>24168</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8033</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18943</t>
+          <t>19192</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23156</t>
+          <t>23409</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>10297</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21092</t>
+          <t>20908</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16583</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20204</t>
+          <t>20063</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34845</t>
+          <t>34482</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,61%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18778</t>
+          <t>18636</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31023</t>
+          <t>30715</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15856</t>
+          <t>15382</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27361</t>
+          <t>27161</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37475</t>
+          <t>37829</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53348</t>
+          <t>54221</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13791</t>
+          <t>13959</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>4807</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14113</t>
+          <t>13403</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>12059</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24258</t>
+          <t>24703</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>9890</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12712</t>
+          <t>12647</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>7555</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>576</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>71387</t>
+          <t>71501</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96375</t>
+          <t>95815</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53626</t>
+          <t>54046</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76799</t>
+          <t>76261</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>131401</t>
+          <t>132584</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>164837</t>
+          <t>166964</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>116210</t>
+          <t>116890</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>144178</t>
+          <t>144807</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>102097</t>
+          <t>102775</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>128459</t>
+          <t>128394</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>227655</t>
+          <t>227618</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>266108</t>
+          <t>266085</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,38%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42738</t>
+          <t>42339</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>63346</t>
+          <t>63512</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>79686</t>
+          <t>79948</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>105234</t>
+          <t>105658</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>130913</t>
+          <t>128052</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>164314</t>
+          <t>162636</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>19189</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>11027</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23309</t>
+          <t>24232</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21530</t>
+          <t>21556</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38895</t>
+          <t>39480</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17042</t>
+          <t>17225</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12608</t>
+          <t>13040</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25836</t>
+          <t>27336</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21122</t>
+          <t>21767</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38634</t>
+          <t>39169</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de gustarle ir al colegio en 2012 (tasa de respuesta: 95,2%)</t>
+          <t>Menores según la frecuencia de gustarle ir al colegio en 2012 (tasa de respuesta: 95,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15456</t>
+          <t>14774</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27049</t>
+          <t>26512</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15876</t>
+          <t>15589</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27196</t>
+          <t>27022</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32830</t>
+          <t>34318</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49473</t>
+          <t>49734</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,39%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11647</t>
+          <t>11419</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23092</t>
+          <t>23273</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18386</t>
+          <t>17419</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22354</t>
+          <t>22222</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37151</t>
+          <t>37297</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,53%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13054</t>
+          <t>12736</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>3371</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11189</t>
+          <t>11415</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8776</t>
+          <t>8984</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20744</t>
+          <t>21410</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1391</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7625</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5717</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11124</t>
+          <t>11137</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>672</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>6671</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>5777</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>10069</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58066</t>
+          <t>58267</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80174</t>
+          <t>79316</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60722</t>
+          <t>58959</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83107</t>
+          <t>83343</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>123417</t>
+          <t>124929</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>155890</t>
+          <t>156097</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70853</t>
+          <t>70447</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92921</t>
+          <t>93318</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63771</t>
+          <t>63721</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86272</t>
+          <t>86666</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>140989</t>
+          <t>141850</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>172855</t>
+          <t>175534</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,59%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27374</t>
+          <t>27595</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45976</t>
+          <t>46822</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39847</t>
+          <t>39922</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60194</t>
+          <t>59930</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>71843</t>
+          <t>72381</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>99580</t>
+          <t>99491</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12701</t>
+          <t>12889</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22212</t>
+          <t>22918</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16221</t>
+          <t>15728</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30761</t>
+          <t>31386</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2387</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10118</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18671</t>
+          <t>18087</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>11938</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24855</t>
+          <t>25343</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23433</t>
+          <t>23979</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36640</t>
+          <t>36593</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9641</t>
+          <t>9493</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21013</t>
+          <t>20828</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36224</t>
+          <t>36926</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53870</t>
+          <t>53894</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,33%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9438</t>
+          <t>9189</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21127</t>
+          <t>20628</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21137</t>
+          <t>21184</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33666</t>
+          <t>33829</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32965</t>
+          <t>34167</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50843</t>
+          <t>51024</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,86%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18054</t>
+          <t>18114</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15759</t>
+          <t>16346</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15993</t>
+          <t>17082</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31176</t>
+          <t>31131</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>671</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>9493</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3561</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>5567</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>104600</t>
+          <t>105430</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>132757</t>
+          <t>132903</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>94179</t>
+          <t>91624</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>122069</t>
+          <t>121567</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>206927</t>
+          <t>205937</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>246981</t>
+          <t>247934</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>39,03%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>100780</t>
+          <t>99071</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>127580</t>
+          <t>128486</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>100838</t>
+          <t>101430</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>130016</t>
+          <t>129835</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>207403</t>
+          <t>208681</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>247616</t>
+          <t>249088</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,22%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>46179</t>
+          <t>46144</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67586</t>
+          <t>69547</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>54481</t>
+          <t>55101</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>79442</t>
+          <t>79226</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>105338</t>
+          <t>106391</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>138847</t>
+          <t>137411</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19885</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13888</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28119</t>
+          <t>29228</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25019</t>
+          <t>24852</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>44637</t>
+          <t>43091</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>16002</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10167</t>
+          <t>10598</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22241</t>
+          <t>23063</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17850</t>
+          <t>16910</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>35025</t>
+          <t>32647</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de gustarle ir al colegio en 2016 (tasa de respuesta: 95,57%)</t>
+          <t>Menores según la frecuencia de gustarle ir al colegio en 2016 (tasa de respuesta: 95,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12531</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>7963</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17805</t>
+          <t>17136</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14540</t>
+          <t>14695</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28075</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,21%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9714</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18819</t>
+          <t>18916</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10923</t>
+          <t>10792</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21259</t>
+          <t>20732</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23013</t>
+          <t>23854</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36771</t>
+          <t>37618</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>55,94%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>8065</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10185</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15423</t>
+          <t>15845</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2513</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5708</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>665</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>6611</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4237</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>9572</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76307</t>
+          <t>74443</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100521</t>
+          <t>99827</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56721</t>
+          <t>55709</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80024</t>
+          <t>78781</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138947</t>
+          <t>138066</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>173715</t>
+          <t>171393</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81095</t>
+          <t>82260</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>106910</t>
+          <t>108489</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81709</t>
+          <t>82046</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>108170</t>
+          <t>107252</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168960</t>
+          <t>169370</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>205647</t>
+          <t>205181</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,77%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30597</t>
+          <t>30338</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49999</t>
+          <t>49517</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43964</t>
+          <t>44399</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64748</t>
+          <t>65498</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>79411</t>
+          <t>80810</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>108427</t>
+          <t>108987</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9257</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20885</t>
+          <t>21488</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>8047</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19840</t>
+          <t>19604</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20186</t>
+          <t>20337</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37293</t>
+          <t>37322</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14565</t>
+          <t>14943</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>3580</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>12797</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10128</t>
+          <t>10942</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22972</t>
+          <t>23327</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19717</t>
+          <t>19449</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33297</t>
+          <t>34127</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19204</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32257</t>
+          <t>32100</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43084</t>
+          <t>42230</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61964</t>
+          <t>61723</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,11%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17487</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31258</t>
+          <t>31765</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24883</t>
+          <t>25642</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>39379</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46161</t>
+          <t>47083</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67061</t>
+          <t>66929</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,66%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>10647</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21918</t>
+          <t>21246</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7660</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18163</t>
+          <t>17476</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19539</t>
+          <t>20221</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35569</t>
+          <t>35751</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>815</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7326</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8802</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13672</t>
+          <t>12270</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>580</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9636</t>
+          <t>8447</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>109354</t>
+          <t>108933</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>138006</t>
+          <t>138204</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>90126</t>
+          <t>91587</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>118410</t>
+          <t>120178</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>207309</t>
+          <t>209057</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>247274</t>
+          <t>249318</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,95%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>117067</t>
+          <t>117083</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>146554</t>
+          <t>147006</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>127357</t>
+          <t>127977</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>157520</t>
+          <t>158094</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>254266</t>
+          <t>251008</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>297069</t>
+          <t>295886</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>48050</t>
+          <t>48006</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>70161</t>
+          <t>71175</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>59817</t>
+          <t>60416</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>85350</t>
+          <t>85433</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>114154</t>
+          <t>114904</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>147919</t>
+          <t>148096</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>12090</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26772</t>
+          <t>26269</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>12441</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26414</t>
+          <t>27065</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28203</t>
+          <t>27821</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>46976</t>
+          <t>48002</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7947</t>
+          <t>7530</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19324</t>
+          <t>19186</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>17464</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16350</t>
+          <t>17126</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32282</t>
+          <t>32527</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
